--- a/KURIKULUM2026_REVISI/037_BOUNDARY_OF_TOPICS_DAN_MATRIKS_ANTI_OVERLAP_KURIKULUM.xlsx
+++ b/KURIKULUM2026_REVISI/037_BOUNDARY_OF_TOPICS_DAN_MATRIKS_ANTI_OVERLAP_KURIKULUM.xlsx
@@ -817,14 +817,14 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Menguasai pemodelan data tabular klasik; menyerahkan data tak terstruktur (citra/sekuensial) ke `STI-626`.</t>
+          <t>Menguasai pemodelan data tabular klasik; menyerahkan data tak terstruktur (citra/sekuensial) ke `STI-726`.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>**`STI-626`**</t>
+          <t>**`STI-726`**</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Menjamin model AI yang dibangun di `STI-413` dan `STI-626` dapat beroperasi andal di lingkungan produksi secara otomatis.</t>
+          <t>Menjamin model AI yang dibangun di `STI-413` dan `STI-726` dapat beroperasi andal di lingkungan produksi secara otomatis.</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Menghasilkan layanan backend modular; menyerahkan aksesibilitas pada perangkat genggam ke `STI-522` dan skalabilitas terdistribusi ke `STI-627`.</t>
+          <t>Menghasilkan layanan backend modular; menyerahkan aksesibilitas pada perangkat genggam ke `STI-522` dan skalabilitas terdistribusi ke `STI-727`.</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>**`STI-627`**</t>
+          <t>**`STI-727`**</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
-          <t>❌ **Dilarang:** Metode numerik klasik (Bisection, Newton-Raphson, Spline, Romberg, RK4); dilarang training CNN/RNN penuh (`STI-626`); dilarang dashboard BI relasional semata (`STI-415`).</t>
+          <t>❌ **Dilarang:** Metode numerik klasik (Bisection, Newton-Raphson, Spline, Romberg, RK4); dilarang training CNN/RNN penuh (`STI-726`); dilarang dashboard BI relasional semata (`STI-415`).</t>
         </is>
       </c>
       <c r="H61" s="8" t="inlineStr">
@@ -2109,7 +2109,7 @@
     <row r="63" ht="16" customHeight="1">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>**`STA-701`**&lt;br&gt;MLOps and AI Pipeline&lt;br&gt;(3 SKS / Sem 7 / +P)&lt;br&gt;*Prasyarat: STI-626 &amp; STI-417*</t>
+          <t>**`STA-701`**&lt;br&gt;MLOps and AI Pipeline&lt;br&gt;(3 SKS / Sem 7 / +P)&lt;br&gt;*Prasyarat: STI-726 &amp; STI-417*</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>**Rasional:** Menegaskan batas tegas antara riset/pelatihan arsitektur model AI (`STI-413`/`STI-626`) dengan rekayasa perangkat lunak operasional untuk deployment, versioning, dan monitoring model di tingkat produksi.</t>
+          <t>**Rasional:** Menegaskan batas tegas antara riset/pelatihan arsitektur model AI (`STI-413`/`STI-726`) dengan rekayasa perangkat lunak operasional untuk deployment, versioning, dan monitoring model di tingkat produksi.</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Mengubah bobot model teroptimasi dari `STI-413`/`STI-626` menjadi artefak layanan web andal siap pakai di skala cloud.</t>
+          <t>Mengubah bobot model teroptimasi dari `STI-413`/`STI-726` menjadi artefak layanan web andal siap pakai di skala cloud.</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
     <row r="65" ht="16" customHeight="1">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>**`STA-703`**&lt;br&gt;Smart Surveillance &amp; IoT Analytics&lt;br&gt;(3 SKS / Sem 7 / +P)&lt;br&gt;*Prasyarat: STI-521 &amp; STI-626*</t>
+          <t>**`STA-703`**&lt;br&gt;Smart Surveillance &amp; IoT Analytics&lt;br&gt;(3 SKS / Sem 7 / +P)&lt;br&gt;*Prasyarat: STI-521 &amp; STI-726*</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>**Rasional:** Menggabungkan visi komputer tingkat lanjut (`STI-626`) dengan komunikasi sensor IoT (`STI-521`) khusus pada ranah analitik video cerdas dan pemantauan otomatis di lingkungan edge/embedded.</t>
+          <t>**Rasional:** Menggabungkan visi komputer tingkat lanjut (`STI-726`) dengan komunikasi sensor IoT (`STI-521`) khusus pada ranah analitik video cerdas dan pemantauan otomatis di lingkungan edge/embedded.</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -2769,7 +2769,7 @@
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>**`STC-702`**&lt;br&gt;SaaS Architecture &amp; Multi-Tenancy&lt;br&gt;(3 SKS / Sem 7 / +P)&lt;br&gt;*Prasyarat: STI-627*</t>
+          <t>**`STC-702`**&lt;br&gt;SaaS Architecture &amp; Multi-Tenancy&lt;br&gt;(3 SKS / Sem 7 / +P)&lt;br&gt;*Prasyarat: STI-727*</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>**Rasional:** Mengembangkan kapabilitas arsitektur sistem terdistribusi (`STI-627`) menjadi produk perangkat lunak komersial multi-penyewa (*Software-as-a-Service*) dengan isolasi data ketat dan model monetisasi berbasis langganan.</t>
+          <t>**Rasional:** Mengembangkan kapabilitas arsitektur sistem terdistribusi (`STI-727`) menjadi produk perangkat lunak komersial multi-penyewa (*Software-as-a-Service*) dengan isolasi data ketat dan model monetisasi berbasis langganan.</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
